--- a/feems/feems/package_data/fuel_eu_fuel_table.xlsx
+++ b/feems/feems/package_data/fuel_eu_fuel_table.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keviny/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keviny/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD853A1-B64A-3D49-9583-683CD07A10E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663BC9D8-A5D4-1940-850F-C1B7297D9D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48940" yWindow="4100" windowWidth="27240" windowHeight="16440" xr2:uid="{69A7AF0C-5BEF-1A4D-9555-9BB66375DE7D}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23040" windowHeight="25320" xr2:uid="{69A7AF0C-5BEF-1A4D-9555-9BB66375DE7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="57">
   <si>
     <t>Data sources</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t xml:space="preserve">_GWP100_N2O </t>
+  </si>
+  <si>
+    <t>Gas Turbine</t>
+  </si>
+  <si>
+    <t>Boiler</t>
   </si>
 </sst>
 </file>
@@ -572,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23512E44-E374-984A-964D-161D1A946BBB}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -757,15 +763,15 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <f>K10/C10</f>
+        <f t="shared" ref="J10:J37" si="0">K10/C10</f>
         <v>78.135555555555541</v>
       </c>
       <c r="K10">
-        <f>(1-I10/100)*(F10+G10*$B$1+H10*$B$2)+I10/100*$B$1</f>
+        <f t="shared" ref="K10:K37" si="1">(1-I10/100)*(F10+G10*$B$1+H10*$B$2)+I10/100*$B$1</f>
         <v>3.1644899999999998</v>
       </c>
       <c r="L10">
-        <f>D10+J10</f>
+        <f t="shared" ref="L10:L37" si="2">D10+J10</f>
         <v>91.635555555555541</v>
       </c>
     </row>
@@ -798,15 +804,15 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <f>K11/C11</f>
+        <f t="shared" si="0"/>
         <v>79.049135802469124</v>
       </c>
       <c r="K11">
-        <f>(1-I11/100)*(F11+G11*$B$1+H11*$B$2)+I11/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.2014899999999997</v>
       </c>
       <c r="L11">
-        <f>D11+J11</f>
+        <f t="shared" si="2"/>
         <v>92.249135802469127</v>
       </c>
     </row>
@@ -839,15 +845,15 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <f>K12/C12</f>
+        <f t="shared" si="0"/>
         <v>79.049135802469124</v>
       </c>
       <c r="K12">
-        <f>(1-I12/100)*(F12+G12*$B$1+H12*$B$2)+I12/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.2014899999999997</v>
       </c>
       <c r="L12">
-        <f>D12+J12</f>
+        <f t="shared" si="2"/>
         <v>92.749135802469127</v>
       </c>
     </row>
@@ -880,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <f>K13/C13</f>
+        <f t="shared" si="0"/>
         <v>78.135555555555541</v>
       </c>
       <c r="K13">
-        <f>(1-I13/100)*(F13+G13*$B$1+H13*$B$2)+I13/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.1644899999999998</v>
       </c>
       <c r="L13">
-        <f>D13+J13</f>
+        <f t="shared" si="2"/>
         <v>91.335555555555544</v>
       </c>
     </row>
@@ -921,15 +927,15 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f>K14/C14</f>
+        <f t="shared" si="0"/>
         <v>79.426585365853654</v>
       </c>
       <c r="K14">
-        <f>(1-I14/100)*(F14+G14*$B$1+H14*$B$2)+I14/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.2564899999999999</v>
       </c>
       <c r="L14">
-        <f>D14+J14</f>
+        <f t="shared" si="2"/>
         <v>92.626585365853657</v>
       </c>
     </row>
@@ -962,15 +968,15 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <f>K15/C15</f>
+        <f t="shared" si="0"/>
         <v>78.085121951219506</v>
       </c>
       <c r="K15">
-        <f>(1-I15/100)*(F15+G15*$B$1+H15*$B$2)+I15/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.2014899999999997</v>
       </c>
       <c r="L15">
-        <f>D15+J15</f>
+        <f t="shared" si="2"/>
         <v>91.285121951219509</v>
       </c>
     </row>
@@ -1003,15 +1009,15 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f>K16/C16</f>
+        <f t="shared" si="0"/>
         <v>76.264402810304446</v>
       </c>
       <c r="K16">
-        <f>(1-I16/100)*(F16+G16*$B$1+H16*$B$2)+I16/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.2564899999999999</v>
       </c>
       <c r="L16">
-        <f>D16+J16</f>
+        <f t="shared" si="2"/>
         <v>90.664402810304452</v>
       </c>
     </row>
@@ -1044,15 +1050,15 @@
         <v>3.1</v>
       </c>
       <c r="J17">
-        <f>K17/C17</f>
+        <f t="shared" si="0"/>
         <v>73.559355624999981</v>
       </c>
       <c r="K17">
-        <f>(1-I17/100)*(F17+G17*$B$1+H17*$B$2)+I17/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.5308490699999995</v>
       </c>
       <c r="L17">
-        <f>D17+J17</f>
+        <f t="shared" si="2"/>
         <v>92.059355624999981</v>
       </c>
     </row>
@@ -1085,15 +1091,15 @@
         <v>1.7</v>
       </c>
       <c r="J18">
-        <f>K18/C18</f>
+        <f t="shared" si="0"/>
         <v>66.495197708333336</v>
       </c>
       <c r="K18">
-        <f>(1-I18/100)*(F18+G18*$B$1+H18*$B$2)+I18/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.19176949</v>
       </c>
       <c r="L18">
-        <f>D18+J18</f>
+        <f t="shared" si="2"/>
         <v>84.995197708333336</v>
       </c>
     </row>
@@ -1126,15 +1132,15 @@
         <v>0.2</v>
       </c>
       <c r="J19">
-        <f>K19/C19</f>
+        <f t="shared" si="0"/>
         <v>58.926457083333325</v>
       </c>
       <c r="K19">
-        <f>(1-I19/100)*(F19+G19*$B$1+H19*$B$2)+I19/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>2.8284699399999997</v>
       </c>
       <c r="L19">
-        <f>D19+J19</f>
+        <f t="shared" si="2"/>
         <v>77.426457083333332</v>
       </c>
     </row>
@@ -1167,15 +1173,15 @@
         <v>2.6</v>
       </c>
       <c r="J20">
-        <f>K20/C20</f>
+        <f t="shared" si="0"/>
         <v>71.036442083333327</v>
       </c>
       <c r="K20">
-        <f>(1-I20/100)*(F20+G20*$B$1+H20*$B$2)+I20/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.4097492199999997</v>
       </c>
       <c r="L20">
-        <f>D20+J20</f>
+        <f t="shared" si="2"/>
         <v>89.536442083333327</v>
       </c>
     </row>
@@ -1208,15 +1214,15 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <f>K21/C21</f>
+        <f t="shared" si="0"/>
         <v>57.291666666666664</v>
       </c>
       <c r="K21">
-        <f>(1-I21/100)*(F21+G21*$B$1+H21*$B$2)+I21/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
       <c r="L21">
-        <f>D21+J21</f>
+        <f t="shared" si="2"/>
         <v>75.791666666666657</v>
       </c>
     </row>
@@ -1249,15 +1255,15 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <f>K22/C22</f>
+        <f t="shared" si="0"/>
         <v>65.869565217391298</v>
       </c>
       <c r="K22">
-        <f>(1-I22/100)*(F22+G22*$B$1+H22*$B$2)+I22/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.03</v>
       </c>
       <c r="L22">
-        <f>D22+J22</f>
+        <f t="shared" si="2"/>
         <v>73.669565217391295</v>
       </c>
     </row>
@@ -1290,15 +1296,15 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <f>K23/C23</f>
+        <f t="shared" si="0"/>
         <v>65.217391304347828</v>
       </c>
       <c r="K23">
-        <f>(1-I23/100)*(F23+G23*$B$1+H23*$B$2)+I23/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="L23">
-        <f>D23+J23</f>
+        <f t="shared" si="2"/>
         <v>73.017391304347825</v>
       </c>
     </row>
@@ -1331,15 +1337,15 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <f>K24/C24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K24">
-        <f>(1-I24/100)*(F24+G24*$B$1+H24*$B$2)+I24/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L24">
-        <f>D24+J24</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
     </row>
@@ -1372,15 +1378,15 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <f>K25/C25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25">
-        <f>(1-I25/100)*(F25+G25*$B$1+H25*$B$2)+I25/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L25">
-        <f>D25+J25</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
     </row>
@@ -1413,15 +1419,15 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <f>K26/C26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26">
-        <f>(1-I26/100)*(F26+G26*$B$1+H26*$B$2)+I26/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L26">
-        <f>D26+J26</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
     </row>
@@ -1454,15 +1460,15 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <f>K27/C27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K27">
-        <f>(1-I27/100)*(F27+G27*$B$1+H27*$B$2)+I27/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L27">
-        <f>D27+J27</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
     </row>
@@ -1495,15 +1501,15 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <f>K28/C28</f>
+        <f t="shared" si="0"/>
         <v>71.632663316582907</v>
       </c>
       <c r="K28">
-        <f>(1-I28/100)*(F28+G28*$B$1+H28*$B$2)+I28/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>1.4254899999999999</v>
       </c>
       <c r="L28">
-        <f>D28+J28</f>
+        <f t="shared" si="2"/>
         <v>102.9326633165829</v>
       </c>
     </row>
@@ -1536,15 +1542,15 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <f>K29/C29</f>
+        <f t="shared" si="0"/>
         <v>71.632663316582907</v>
       </c>
       <c r="K29">
-        <f>(1-I29/100)*(F29+G29*$B$1+H29*$B$2)+I29/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>1.4254899999999999</v>
       </c>
       <c r="L29">
-        <f>D29+J29</f>
+        <f t="shared" si="2"/>
         <v>13.278894476582906</v>
       </c>
     </row>
@@ -1577,15 +1583,15 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <f>K30/C30</f>
+        <f t="shared" si="0"/>
         <v>71.380597014925371</v>
       </c>
       <c r="K30">
-        <f>(1-I30/100)*(F30+G30*$B$1+H30*$B$2)+I30/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>1.913</v>
       </c>
       <c r="L30">
-        <f>D30+J30</f>
+        <f t="shared" si="2"/>
         <v>38.180597014925368</v>
       </c>
     </row>
@@ -1618,15 +1624,15 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <f>K31/C31</f>
+        <f t="shared" si="0"/>
         <v>77.540053763440866</v>
       </c>
       <c r="K31">
-        <f>(1-I31/100)*(F31+G31*$B$1+H31*$B$2)+I31/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>2.88449</v>
       </c>
       <c r="L31">
-        <f>D31+J31</f>
+        <f t="shared" si="2"/>
         <v>51.440053763440865</v>
       </c>
     </row>
@@ -1659,15 +1665,15 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <f>K32/C32</f>
+        <f t="shared" si="0"/>
         <v>71.942954545454555</v>
       </c>
       <c r="K32">
-        <f>(1-I32/100)*(F32+G32*$B$1+H32*$B$2)+I32/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.1654900000000001</v>
       </c>
       <c r="L32">
-        <f>D32+J32</f>
+        <f t="shared" si="2"/>
         <v>51.242954545454552</v>
       </c>
     </row>
@@ -1700,15 +1706,15 @@
         <v>3.1</v>
       </c>
       <c r="J33">
-        <f>K33/C33</f>
+        <f t="shared" si="0"/>
         <v>70.616981399999986</v>
       </c>
       <c r="K33">
-        <f>(1-I33/100)*(F33+G33*$B$1+H33*$B$2)+I33/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.5308490699999995</v>
       </c>
       <c r="L33">
-        <f>D33+J33</f>
+        <f t="shared" si="2"/>
         <v>31.716981399999987</v>
       </c>
     </row>
@@ -1741,15 +1747,15 @@
         <v>1.7</v>
       </c>
       <c r="J34">
-        <f>K34/C34</f>
+        <f t="shared" si="0"/>
         <v>63.835389799999994</v>
       </c>
       <c r="K34">
-        <f>(1-I34/100)*(F34+G34*$B$1+H34*$B$2)+I34/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.19176949</v>
       </c>
       <c r="L34">
-        <f>D34+J34</f>
+        <f t="shared" si="2"/>
         <v>24.935389799999996</v>
       </c>
     </row>
@@ -1782,15 +1788,15 @@
         <v>0.2</v>
       </c>
       <c r="J35">
-        <f>K35/C35</f>
+        <f t="shared" si="0"/>
         <v>56.569398799999995</v>
       </c>
       <c r="K35">
-        <f>(1-I35/100)*(F35+G35*$B$1+H35*$B$2)+I35/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>2.8284699399999997</v>
       </c>
       <c r="L35">
-        <f>D35+J35</f>
+        <f t="shared" si="2"/>
         <v>17.669398799999996</v>
       </c>
     </row>
@@ -1823,15 +1829,15 @@
         <v>2.6</v>
       </c>
       <c r="J36">
-        <f>K36/C36</f>
+        <f t="shared" si="0"/>
         <v>68.194984399999996</v>
       </c>
       <c r="K36">
-        <f>(1-I36/100)*(F36+G36*$B$1+H36*$B$2)+I36/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>3.4097492199999997</v>
       </c>
       <c r="L36">
-        <f>D36+J36</f>
+        <f t="shared" si="2"/>
         <v>29.294984399999997</v>
       </c>
     </row>
@@ -1864,15 +1870,15 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <f>K37/C37</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="K37">
-        <f>(1-I37/100)*(F37+G37*$B$1+H37*$B$2)+I37/100*$B$1</f>
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
       <c r="L37">
-        <f>D37+J37</f>
+        <f t="shared" si="2"/>
         <v>16.100000000000001</v>
       </c>
     </row>
@@ -1928,15 +1934,15 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <f>K39/C39</f>
+        <f t="shared" ref="J39:J51" si="3">K39/C39</f>
         <v>0</v>
       </c>
       <c r="K39">
-        <f>(1-I39/100)*(F39+G39*$B$1+H39*$B$2)+I39/100*$B$1</f>
+        <f t="shared" ref="K39:K51" si="4">(1-I39/100)*(F39+G39*$B$1+H39*$B$2)+I39/100*$B$1</f>
         <v>0</v>
       </c>
       <c r="L39">
-        <f>D39+J39</f>
+        <f t="shared" ref="L39:L49" si="5">D39+J39</f>
         <v>0</v>
       </c>
     </row>
@@ -1969,15 +1975,15 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <f>K40/C40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K40">
-        <f>(1-I40/100)*(F40+G40*$B$1+H40*$B$2)+I40/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L40">
-        <f>D40+J40</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2010,15 +2016,15 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <f>K41/C41</f>
+        <f t="shared" si="3"/>
         <v>76.264402810304446</v>
       </c>
       <c r="K41">
-        <f>(1-I41/100)*(F41+G41*$B$1+H41*$B$2)+I41/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>3.2564899999999999</v>
       </c>
       <c r="L41">
-        <f>D41+J41</f>
+        <f t="shared" si="5"/>
         <v>28.664402810304445</v>
       </c>
     </row>
@@ -2051,15 +2057,15 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <f>K42/C42</f>
+        <f t="shared" si="3"/>
         <v>71.632663316582907</v>
       </c>
       <c r="K42">
-        <f>(1-I42/100)*(F42+G42*$B$1+H42*$B$2)+I42/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>1.4254899999999999</v>
       </c>
       <c r="L42">
-        <f>D42+J42</f>
+        <f t="shared" si="5"/>
         <v>4.5326633165829122</v>
       </c>
     </row>
@@ -2092,15 +2098,15 @@
         <v>3.1</v>
       </c>
       <c r="J43">
-        <f>K43/C43</f>
+        <f t="shared" si="3"/>
         <v>71.911386354378806</v>
       </c>
       <c r="K43">
-        <f>(1-I43/100)*(F43+G43*$B$1+H43*$B$2)+I43/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>3.5308490699999995</v>
       </c>
       <c r="L43">
-        <f>D43+J43</f>
+        <f t="shared" si="5"/>
         <v>45.311386354378804</v>
       </c>
     </row>
@@ -2133,15 +2139,15 @@
         <v>1.7</v>
       </c>
       <c r="J44">
-        <f>K44/C44</f>
+        <f t="shared" si="3"/>
         <v>65.005488594704687</v>
       </c>
       <c r="K44">
-        <f>(1-I44/100)*(F44+G44*$B$1+H44*$B$2)+I44/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>3.19176949</v>
       </c>
       <c r="L44">
-        <f>D44+J44</f>
+        <f t="shared" si="5"/>
         <v>38.405488594704686</v>
       </c>
     </row>
@@ -2174,15 +2180,15 @@
         <v>0.2</v>
       </c>
       <c r="J45">
-        <f>K45/C45</f>
+        <f t="shared" si="3"/>
         <v>57.606312423625255</v>
       </c>
       <c r="K45">
-        <f>(1-I45/100)*(F45+G45*$B$1+H45*$B$2)+I45/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>2.8284699399999997</v>
       </c>
       <c r="L45">
-        <f>D45+J45</f>
+        <f t="shared" si="5"/>
         <v>31.006312423625253</v>
       </c>
     </row>
@@ -2215,15 +2221,15 @@
         <v>2.6</v>
       </c>
       <c r="J46">
-        <f>K46/C46</f>
+        <f t="shared" si="3"/>
         <v>69.444994297352338</v>
       </c>
       <c r="K46">
-        <f>(1-I46/100)*(F46+G46*$B$1+H46*$B$2)+I46/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>3.4097492199999997</v>
       </c>
       <c r="L46">
-        <f>D46+J46</f>
+        <f t="shared" si="5"/>
         <v>42.844994297352336</v>
       </c>
     </row>
@@ -2256,15 +2262,15 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <f>K47/C47</f>
+        <f t="shared" si="3"/>
         <v>56.008146639511203</v>
       </c>
       <c r="K47">
-        <f>(1-I47/100)*(F47+G47*$B$1+H47*$B$2)+I47/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>2.75</v>
       </c>
       <c r="L47">
-        <f>D47+J47</f>
+        <f t="shared" si="5"/>
         <v>29.408146639511202</v>
       </c>
     </row>
@@ -2297,15 +2303,15 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <f>K48/C48</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K48">
-        <f>(1-I48/100)*(F48+G48*$B$1+H48*$B$2)+I48/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L48">
-        <f>D48+J48</f>
+        <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
     </row>
@@ -2338,15 +2344,15 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <f>K49/C49</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K49">
-        <f>(1-I49/100)*(F49+G49*$B$1+H49*$B$2)+I49/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L49">
-        <f>D49+J49</f>
+        <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
     </row>
@@ -2379,11 +2385,11 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <f>K50/C50</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K50">
-        <f>(1-I50/100)*(F50+G50*$B$1+H50*$B$2)+I50/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L50">
@@ -2419,11 +2425,11 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <f>K51/C51</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K51">
-        <f>(1-I51/100)*(F51+G51*$B$1+H51*$B$2)+I51/100*$B$1</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L51">
@@ -2480,27 +2486,1492 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D55">
+        <v>18.5</v>
+      </c>
+      <c r="E55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55">
+        <v>2.75</v>
+      </c>
+      <c r="G55">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H55">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I55">
+        <v>0.01</v>
+      </c>
+      <c r="J55">
+        <f t="shared" ref="J55" si="6">K55/C55</f>
+        <v>57.72314939999999</v>
+      </c>
+      <c r="K55">
+        <f t="shared" ref="K55" si="7">(1-I55/100)*(F55+G55*$B$1+H55*$B$2)+I55/100*$B$1</f>
+        <v>2.7707111711999994</v>
+      </c>
+      <c r="L55">
+        <f t="shared" ref="L55" si="8">D55+J55</f>
+        <v>76.223149399999983</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56">
+        <v>0.05</v>
+      </c>
+      <c r="D56">
+        <v>-38.9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56">
+        <v>2.75</v>
+      </c>
+      <c r="G56">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H56">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I56">
+        <v>0.01</v>
+      </c>
+      <c r="J56">
+        <f t="shared" ref="J56:J93" si="9">K56/C56</f>
+        <v>55.414223423999985</v>
+      </c>
+      <c r="K56">
+        <f t="shared" ref="K56:K93" si="10">(1-I56/100)*(F56+G56*$B$1+H56*$B$2)+I56/100*$B$1</f>
+        <v>2.7707111711999994</v>
+      </c>
+      <c r="L56">
+        <f t="shared" ref="L56:L93" si="11">D56+J56</f>
+        <v>16.514223423999987</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="D57">
+        <v>-26.6</v>
+      </c>
+      <c r="E57" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57">
+        <v>2.75</v>
+      </c>
+      <c r="G57">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H57">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I57">
+        <v>0.01</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="9"/>
+        <v>56.429962753564148</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="10"/>
+        <v>2.7707111711999994</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="11"/>
+        <v>29.829962753564146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="D58">
+        <v>14.4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58">
+        <v>3.206</v>
+      </c>
+      <c r="G58">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H58">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I58">
+        <v>0.01</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="9"/>
+        <v>75.565938435597175</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="10"/>
+        <v>3.2266655711999994</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="11"/>
+        <v>89.965938435597181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="D59">
+        <v>-26.1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59">
+        <v>2.8340000000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H59">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I59">
+        <v>0.01</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="9"/>
+        <v>76.739321806451599</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="10"/>
+        <v>2.8547027711999995</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="11"/>
+        <v>50.639321806451598</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="D60">
+        <v>-47.6</v>
+      </c>
+      <c r="E60" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60">
+        <v>3.206</v>
+      </c>
+      <c r="G60">
+        <v>1.92E-4</v>
+      </c>
+      <c r="H60">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="I60">
+        <v>0.01</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="9"/>
+        <v>75.565938435597175</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="10"/>
+        <v>3.2266655711999994</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="11"/>
+        <v>27.965938435597174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>0.12</v>
+      </c>
+      <c r="D61">
+        <v>132</v>
+      </c>
+      <c r="E61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="11"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62">
+        <v>0.12</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
+        <v>55</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63">
+        <v>0.12</v>
+      </c>
+      <c r="D63">
+        <v>3.6</v>
+      </c>
+      <c r="E63" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="11"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>55</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="D65">
+        <v>13.5</v>
+      </c>
+      <c r="E65" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65">
+        <v>3.1139999999999999</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="9"/>
+        <v>78.10222222222221</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="10"/>
+        <v>3.1631399999999998</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="11"/>
+        <v>91.60222222222221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="D66">
+        <v>13.2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66">
+        <v>3.1509999999999998</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="9"/>
+        <v>79.015802469135792</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="10"/>
+        <v>3.2001399999999998</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="11"/>
+        <v>92.215802469135795</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="D67">
+        <v>13.7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>56</v>
+      </c>
+      <c r="F67">
+        <v>3.1509999999999998</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="9"/>
+        <v>79.015802469135792</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="10"/>
+        <v>3.2001399999999998</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="11"/>
+        <v>92.715802469135795</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="D68">
+        <v>13.2</v>
+      </c>
+      <c r="E68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F68">
+        <v>3.1139999999999999</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="9"/>
+        <v>78.10222222222221</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="10"/>
+        <v>3.1631399999999998</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="11"/>
+        <v>91.302222222222213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D69">
+        <v>13.2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69">
+        <v>3.206</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="9"/>
+        <v>79.393658536585363</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="10"/>
+        <v>3.2551399999999999</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="11"/>
+        <v>92.593658536585366</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D70">
+        <v>13.2</v>
+      </c>
+      <c r="E70" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70">
+        <v>3.1509999999999998</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="9"/>
+        <v>78.052195121951215</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="10"/>
+        <v>3.2001399999999998</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="11"/>
+        <v>91.252195121951218</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="D71">
+        <v>14.4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71">
+        <v>3.206</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="9"/>
+        <v>76.232786885245901</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="10"/>
+        <v>3.2551399999999999</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="11"/>
+        <v>90.632786885245906</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>26</v>
+      </c>
+      <c r="B72" t="s">
+        <v>35</v>
+      </c>
+      <c r="C72">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D72">
+        <v>18.5</v>
+      </c>
+      <c r="E72" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72">
+        <v>2.75</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>1.1E-4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="9"/>
+        <v>57.917291666666664</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="10"/>
+        <v>2.78003</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="11"/>
+        <v>76.417291666666671</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D73">
+        <v>7.8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73">
+        <v>3.03</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="9"/>
+        <v>65.869565217391298</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="10"/>
+        <v>3.03</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="11"/>
+        <v>73.669565217391295</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D74">
+        <v>7.8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>56</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="9"/>
+        <v>65.217391304347828</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="11"/>
+        <v>73.017391304347825</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75">
+        <v>0.12</v>
+      </c>
+      <c r="D75">
+        <v>132</v>
+      </c>
+      <c r="E75" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="11"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="D76">
+        <v>121</v>
+      </c>
+      <c r="E76" t="s">
+        <v>56</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="11"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="D77">
+        <v>31.3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77">
+        <v>1.375</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="9"/>
+        <v>71.564824120603006</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="10"/>
+        <v>1.42414</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="11"/>
+        <v>102.864824120603</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>46</v>
+      </c>
+      <c r="B78" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="D78">
+        <v>-58.353768840000001</v>
+      </c>
+      <c r="E78" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78">
+        <v>1.375</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="9"/>
+        <v>71.564824120603006</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="10"/>
+        <v>1.42414</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="11"/>
+        <v>13.211055280603006</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="D79">
+        <v>-33.200000000000003</v>
+      </c>
+      <c r="E79" t="s">
+        <v>56</v>
+      </c>
+      <c r="F79">
+        <v>1.913</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="9"/>
+        <v>71.380597014925371</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="10"/>
+        <v>1.913</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="11"/>
+        <v>38.180597014925368</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="D80">
+        <v>-26.1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>56</v>
+      </c>
+      <c r="F80">
+        <v>2.8340000000000001</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="9"/>
+        <v>77.503763440860226</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="10"/>
+        <v>2.88314</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="11"/>
+        <v>51.403763440860224</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D81">
+        <v>-20.7</v>
+      </c>
+      <c r="E81" t="s">
+        <v>56</v>
+      </c>
+      <c r="F81">
+        <v>3.1150000000000002</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="9"/>
+        <v>71.912272727272736</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="10"/>
+        <v>3.1641400000000002</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="11"/>
+        <v>51.212272727272733</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>46</v>
+      </c>
+      <c r="B82" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82">
+        <v>0.05</v>
+      </c>
+      <c r="D82">
+        <v>-38.9</v>
+      </c>
+      <c r="E82" t="s">
+        <v>56</v>
+      </c>
+      <c r="F82">
+        <v>2.75</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>1.1E-4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="9"/>
+        <v>55.6006</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="10"/>
+        <v>2.78003</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="11"/>
+        <v>16.700600000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>46</v>
+      </c>
+      <c r="B83" t="s">
+        <v>49</v>
+      </c>
+      <c r="E83" t="s">
+        <v>56</v>
+      </c>
+      <c r="F83">
+        <v>3.1150000000000002</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>46</v>
+      </c>
+      <c r="B84" t="s">
+        <v>43</v>
+      </c>
+      <c r="C84">
+        <v>0.12</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
+        <v>56</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="D85">
+        <v>-47.6</v>
+      </c>
+      <c r="E85" t="s">
+        <v>56</v>
+      </c>
+      <c r="F85">
+        <v>3.206</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="9"/>
+        <v>76.232786885245901</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="10"/>
+        <v>3.2551399999999999</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="11"/>
+        <v>28.632786885245899</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="D86">
+        <v>-67.099999999999994</v>
+      </c>
+      <c r="E86" t="s">
+        <v>56</v>
+      </c>
+      <c r="F86">
+        <v>1.375</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="9"/>
+        <v>71.564824120603006</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="10"/>
+        <v>1.42414</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="11"/>
+        <v>4.4648241206030121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="D87">
+        <v>-26.6</v>
+      </c>
+      <c r="E87" t="s">
+        <v>56</v>
+      </c>
+      <c r="F87">
+        <v>2.75</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>1.1E-4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="9"/>
+        <v>56.619755600814663</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="10"/>
+        <v>2.78003</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="11"/>
+        <v>30.019755600814662</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88">
+        <v>0.12</v>
+      </c>
+      <c r="D88">
+        <v>3.6</v>
+      </c>
+      <c r="E88" t="s">
+        <v>56</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="11"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>56</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>41</v>
+      </c>
+      <c r="C90">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>50</v>
+      </c>
+      <c r="D92">
+        <v>1.7</v>
+      </c>
+      <c r="E92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>51</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B93" t="s">
         <v>51</v>
       </c>
-      <c r="D55">
+      <c r="D93">
         <v>70.555555560000002</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E93" t="s">
         <v>52</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
         <v>0</v>
       </c>
     </row>
